--- a/product_selector_out/STM8S103-105.xlsx
+++ b/product_selector_out/STM8S103-105.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,8 @@
     <col width="23.46484375" customWidth="1" min="30" max="30"/>
     <col width="11.6328125" customWidth="1" min="31" max="31"/>
     <col width="43.6484375" customWidth="1" min="32" max="32"/>
-    <col width="52" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="52" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -716,6 +717,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -883,6 +889,11 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -1050,6 +1061,11 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -1217,6 +1233,11 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s105c4.pdf</t>
         </is>
       </c>
@@ -1384,6 +1405,11 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -1551,6 +1577,11 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -1718,6 +1749,11 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -1885,6 +1921,11 @@
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -2052,6 +2093,11 @@
       </c>
       <c r="AG18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
@@ -2219,14 +2265,19 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8s103f2.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
@@ -2250,7 +2301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2286,6 +2337,7 @@
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2472,6 +2524,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -2637,7 +2694,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AG11" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -2804,7 +2866,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -2971,7 +3038,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="6" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3138,7 +3210,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="6" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3305,7 +3382,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="6" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3472,7 +3554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="6" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3639,7 +3726,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="6" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3806,7 +3898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="6" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3973,7 +4070,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="6" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3981,8 +4083,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
